--- a/artfynd/A 64610-2023 artfynd.xlsx
+++ b/artfynd/A 64610-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951626</v>
       </c>
       <c r="B2" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957695</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957699</v>
       </c>
       <c r="B4" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951627</v>
       </c>
       <c r="B5" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136951628</v>
       </c>
       <c r="B6" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136951630</v>
       </c>
       <c r="B7" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136951631</v>
       </c>
       <c r="B8" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136957696</v>
       </c>
       <c r="B9" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136957697</v>
       </c>
       <c r="B10" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136957700</v>
       </c>
       <c r="B11" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136957698</v>
       </c>
       <c r="B12" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136951629</v>
       </c>
       <c r="B13" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>136957694</v>
       </c>
       <c r="B14" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 64610-2023 artfynd.xlsx
+++ b/artfynd/A 64610-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951626</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957695</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957699</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951627</v>
       </c>
       <c r="B5" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136951628</v>
       </c>
       <c r="B6" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136951630</v>
       </c>
       <c r="B7" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136951631</v>
       </c>
       <c r="B8" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136957696</v>
       </c>
       <c r="B9" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136957697</v>
       </c>
       <c r="B10" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136957700</v>
       </c>
       <c r="B11" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136957698</v>
       </c>
       <c r="B12" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136951629</v>
       </c>
       <c r="B13" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>136957694</v>
       </c>
       <c r="B14" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 64610-2023 artfynd.xlsx
+++ b/artfynd/A 64610-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951626</v>
       </c>
       <c r="B2" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957695</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957699</v>
       </c>
       <c r="B4" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951627</v>
       </c>
       <c r="B5" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136951628</v>
       </c>
       <c r="B6" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136951630</v>
       </c>
       <c r="B7" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136951631</v>
       </c>
       <c r="B8" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136957696</v>
       </c>
       <c r="B9" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136957697</v>
       </c>
       <c r="B10" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136957700</v>
       </c>
       <c r="B11" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136957698</v>
       </c>
       <c r="B12" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136951629</v>
       </c>
       <c r="B13" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>136957694</v>
       </c>
       <c r="B14" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 64610-2023 artfynd.xlsx
+++ b/artfynd/A 64610-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951626</v>
       </c>
       <c r="B2" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957695</v>
       </c>
       <c r="B3" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957699</v>
       </c>
       <c r="B4" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951627</v>
       </c>
       <c r="B5" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136951628</v>
       </c>
       <c r="B6" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136951630</v>
       </c>
       <c r="B7" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136951631</v>
       </c>
       <c r="B8" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136957696</v>
       </c>
       <c r="B9" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136957697</v>
       </c>
       <c r="B10" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136957700</v>
       </c>
       <c r="B11" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136957698</v>
       </c>
       <c r="B12" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136951629</v>
       </c>
       <c r="B13" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>136957694</v>
       </c>
       <c r="B14" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 64610-2023 artfynd.xlsx
+++ b/artfynd/A 64610-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951626</v>
       </c>
       <c r="B2" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957695</v>
       </c>
       <c r="B3" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957699</v>
       </c>
       <c r="B4" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951627</v>
       </c>
       <c r="B5" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136951628</v>
       </c>
       <c r="B6" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136951630</v>
       </c>
       <c r="B7" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136951631</v>
       </c>
       <c r="B8" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136957696</v>
       </c>
       <c r="B9" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136957697</v>
       </c>
       <c r="B10" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136957700</v>
       </c>
       <c r="B11" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136957698</v>
       </c>
       <c r="B12" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136951629</v>
       </c>
       <c r="B13" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>136957694</v>
       </c>
       <c r="B14" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 64610-2023 artfynd.xlsx
+++ b/artfynd/A 64610-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951626</v>
       </c>
       <c r="B2" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957695</v>
       </c>
       <c r="B3" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957699</v>
       </c>
       <c r="B4" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951627</v>
       </c>
       <c r="B5" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136951628</v>
       </c>
       <c r="B6" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136951630</v>
       </c>
       <c r="B7" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136951631</v>
       </c>
       <c r="B8" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136957696</v>
       </c>
       <c r="B9" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136957697</v>
       </c>
       <c r="B10" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136957700</v>
       </c>
       <c r="B11" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136957698</v>
       </c>
       <c r="B12" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136951629</v>
       </c>
       <c r="B13" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>136957694</v>
       </c>
       <c r="B14" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 64610-2023 artfynd.xlsx
+++ b/artfynd/A 64610-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951626</v>
       </c>
       <c r="B2" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957695</v>
       </c>
       <c r="B3" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957699</v>
       </c>
       <c r="B4" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951627</v>
       </c>
       <c r="B5" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136951628</v>
       </c>
       <c r="B6" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136951630</v>
       </c>
       <c r="B7" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136951631</v>
       </c>
       <c r="B8" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136957696</v>
       </c>
       <c r="B9" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136957697</v>
       </c>
       <c r="B10" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136957700</v>
       </c>
       <c r="B11" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136957698</v>
       </c>
       <c r="B12" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136951629</v>
       </c>
       <c r="B13" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>136957694</v>
       </c>
       <c r="B14" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 64610-2023 artfynd.xlsx
+++ b/artfynd/A 64610-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951626</v>
       </c>
       <c r="B2" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957695</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957699</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951627</v>
       </c>
       <c r="B5" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136951628</v>
       </c>
       <c r="B6" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136951630</v>
       </c>
       <c r="B7" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136951631</v>
       </c>
       <c r="B8" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136957696</v>
       </c>
       <c r="B9" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136957697</v>
       </c>
       <c r="B10" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136957700</v>
       </c>
       <c r="B11" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136957698</v>
       </c>
       <c r="B12" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136951629</v>
       </c>
       <c r="B13" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>136957694</v>
       </c>
       <c r="B14" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 64610-2023 artfynd.xlsx
+++ b/artfynd/A 64610-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951626</v>
       </c>
       <c r="B2" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957695</v>
       </c>
       <c r="B3" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957699</v>
       </c>
       <c r="B4" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951627</v>
       </c>
       <c r="B5" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136951628</v>
       </c>
       <c r="B6" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136951630</v>
       </c>
       <c r="B7" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136951631</v>
       </c>
       <c r="B8" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136957696</v>
       </c>
       <c r="B9" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136957697</v>
       </c>
       <c r="B10" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136957700</v>
       </c>
       <c r="B11" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136957698</v>
       </c>
       <c r="B12" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136951629</v>
       </c>
       <c r="B13" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>136957694</v>
       </c>
       <c r="B14" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 64610-2023 artfynd.xlsx
+++ b/artfynd/A 64610-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951626</v>
       </c>
       <c r="B2" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957695</v>
       </c>
       <c r="B3" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957699</v>
       </c>
       <c r="B4" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951627</v>
       </c>
       <c r="B5" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136951628</v>
       </c>
       <c r="B6" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136951630</v>
       </c>
       <c r="B7" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136951631</v>
       </c>
       <c r="B8" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136957696</v>
       </c>
       <c r="B9" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136957697</v>
       </c>
       <c r="B10" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136957700</v>
       </c>
       <c r="B11" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136957698</v>
       </c>
       <c r="B12" t="n">
-        <v>108416</v>
+        <v>108421</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136951629</v>
       </c>
       <c r="B13" t="n">
-        <v>99311</v>
+        <v>99314</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>136957694</v>
       </c>
       <c r="B14" t="n">
-        <v>99311</v>
+        <v>99314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 64610-2023 artfynd.xlsx
+++ b/artfynd/A 64610-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951626</v>
       </c>
       <c r="B2" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957695</v>
       </c>
       <c r="B3" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957699</v>
       </c>
       <c r="B4" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951627</v>
       </c>
       <c r="B5" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136951628</v>
       </c>
       <c r="B6" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136951630</v>
       </c>
       <c r="B7" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136951631</v>
       </c>
       <c r="B8" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136957696</v>
       </c>
       <c r="B9" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136957697</v>
       </c>
       <c r="B10" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136957700</v>
       </c>
       <c r="B11" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136957698</v>
       </c>
       <c r="B12" t="n">
-        <v>108421</v>
+        <v>108442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136951629</v>
       </c>
       <c r="B13" t="n">
-        <v>99314</v>
+        <v>99324</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>136957694</v>
       </c>
       <c r="B14" t="n">
-        <v>99314</v>
+        <v>99324</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 64610-2023 artfynd.xlsx
+++ b/artfynd/A 64610-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951626</v>
       </c>
       <c r="B2" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957695</v>
       </c>
       <c r="B3" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957699</v>
       </c>
       <c r="B4" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951627</v>
       </c>
       <c r="B5" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136951628</v>
       </c>
       <c r="B6" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136951630</v>
       </c>
       <c r="B7" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136951631</v>
       </c>
       <c r="B8" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136957696</v>
       </c>
       <c r="B9" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136957697</v>
       </c>
       <c r="B10" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136957700</v>
       </c>
       <c r="B11" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136957698</v>
       </c>
       <c r="B12" t="n">
-        <v>108442</v>
+        <v>108443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136951629</v>
       </c>
       <c r="B13" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>136957694</v>
       </c>
       <c r="B14" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 64610-2023 artfynd.xlsx
+++ b/artfynd/A 64610-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951626</v>
       </c>
       <c r="B2" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957695</v>
       </c>
       <c r="B3" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957699</v>
       </c>
       <c r="B4" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951627</v>
       </c>
       <c r="B5" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136951628</v>
       </c>
       <c r="B6" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136951630</v>
       </c>
       <c r="B7" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136951631</v>
       </c>
       <c r="B8" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136957696</v>
       </c>
       <c r="B9" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136957697</v>
       </c>
       <c r="B10" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136957700</v>
       </c>
       <c r="B11" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136957698</v>
       </c>
       <c r="B12" t="n">
-        <v>108443</v>
+        <v>108448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136951629</v>
       </c>
       <c r="B13" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>136957694</v>
       </c>
       <c r="B14" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 64610-2023 artfynd.xlsx
+++ b/artfynd/A 64610-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951626</v>
       </c>
       <c r="B2" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957695</v>
       </c>
       <c r="B3" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957699</v>
       </c>
       <c r="B4" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951627</v>
       </c>
       <c r="B5" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136951628</v>
       </c>
       <c r="B6" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136951630</v>
       </c>
       <c r="B7" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136951631</v>
       </c>
       <c r="B8" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136957696</v>
       </c>
       <c r="B9" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136957697</v>
       </c>
       <c r="B10" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136957700</v>
       </c>
       <c r="B11" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136957698</v>
       </c>
       <c r="B12" t="n">
-        <v>108448</v>
+        <v>108451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136951629</v>
       </c>
       <c r="B13" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>136957694</v>
       </c>
       <c r="B14" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 64610-2023 artfynd.xlsx
+++ b/artfynd/A 64610-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951626</v>
       </c>
       <c r="B2" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957695</v>
       </c>
       <c r="B3" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957699</v>
       </c>
       <c r="B4" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951627</v>
       </c>
       <c r="B5" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136951628</v>
       </c>
       <c r="B6" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136951630</v>
       </c>
       <c r="B7" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136951631</v>
       </c>
       <c r="B8" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136957696</v>
       </c>
       <c r="B9" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136957697</v>
       </c>
       <c r="B10" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136957700</v>
       </c>
       <c r="B11" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136957698</v>
       </c>
       <c r="B12" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136951629</v>
       </c>
       <c r="B13" t="n">
-        <v>99332</v>
+        <v>99338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>136957694</v>
       </c>
       <c r="B14" t="n">
-        <v>99332</v>
+        <v>99338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 64610-2023 artfynd.xlsx
+++ b/artfynd/A 64610-2023 artfynd.xlsx
@@ -1743,7 +1743,7 @@
         <v>136957698</v>
       </c>
       <c r="B12" t="n">
-        <v>108457</v>
+        <v>108458</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 64610-2023 artfynd.xlsx
+++ b/artfynd/A 64610-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951626</v>
       </c>
       <c r="B2" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957695</v>
       </c>
       <c r="B3" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957699</v>
       </c>
       <c r="B4" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951627</v>
       </c>
       <c r="B5" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136951628</v>
       </c>
       <c r="B6" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136951630</v>
       </c>
       <c r="B7" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136951631</v>
       </c>
       <c r="B8" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136957696</v>
       </c>
       <c r="B9" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136957697</v>
       </c>
       <c r="B10" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136957700</v>
       </c>
       <c r="B11" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136957698</v>
       </c>
       <c r="B12" t="n">
-        <v>108458</v>
+        <v>108470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136951629</v>
       </c>
       <c r="B13" t="n">
-        <v>99338</v>
+        <v>99350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>136957694</v>
       </c>
       <c r="B14" t="n">
-        <v>99338</v>
+        <v>99350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 64610-2023 artfynd.xlsx
+++ b/artfynd/A 64610-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951626</v>
       </c>
       <c r="B2" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957695</v>
       </c>
       <c r="B3" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957699</v>
       </c>
       <c r="B4" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951627</v>
       </c>
       <c r="B5" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136951628</v>
       </c>
       <c r="B6" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136951630</v>
       </c>
       <c r="B7" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136951631</v>
       </c>
       <c r="B8" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136957696</v>
       </c>
       <c r="B9" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136957697</v>
       </c>
       <c r="B10" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136957700</v>
       </c>
       <c r="B11" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136957698</v>
       </c>
       <c r="B12" t="n">
-        <v>108470</v>
+        <v>108471</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136951629</v>
       </c>
       <c r="B13" t="n">
-        <v>99350</v>
+        <v>99351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>136957694</v>
       </c>
       <c r="B14" t="n">
-        <v>99350</v>
+        <v>99351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 64610-2023 artfynd.xlsx
+++ b/artfynd/A 64610-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951626</v>
       </c>
       <c r="B2" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957695</v>
       </c>
       <c r="B3" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957699</v>
       </c>
       <c r="B4" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951627</v>
       </c>
       <c r="B5" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136951628</v>
       </c>
       <c r="B6" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136951630</v>
       </c>
       <c r="B7" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136951631</v>
       </c>
       <c r="B8" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136957696</v>
       </c>
       <c r="B9" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136957697</v>
       </c>
       <c r="B10" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136957700</v>
       </c>
       <c r="B11" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136957698</v>
       </c>
       <c r="B12" t="n">
-        <v>108471</v>
+        <v>108474</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136951629</v>
       </c>
       <c r="B13" t="n">
-        <v>99351</v>
+        <v>99354</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>136957694</v>
       </c>
       <c r="B14" t="n">
-        <v>99351</v>
+        <v>99354</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 64610-2023 artfynd.xlsx
+++ b/artfynd/A 64610-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951626</v>
       </c>
       <c r="B2" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957695</v>
       </c>
       <c r="B3" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957699</v>
       </c>
       <c r="B4" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951627</v>
       </c>
       <c r="B5" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136951628</v>
       </c>
       <c r="B6" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136951630</v>
       </c>
       <c r="B7" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136951631</v>
       </c>
       <c r="B8" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136957696</v>
       </c>
       <c r="B9" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136957697</v>
       </c>
       <c r="B10" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136957700</v>
       </c>
       <c r="B11" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136957698</v>
       </c>
       <c r="B12" t="n">
-        <v>108474</v>
+        <v>108476</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136951629</v>
       </c>
       <c r="B13" t="n">
-        <v>99354</v>
+        <v>99355</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>136957694</v>
       </c>
       <c r="B14" t="n">
-        <v>99354</v>
+        <v>99355</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 64610-2023 artfynd.xlsx
+++ b/artfynd/A 64610-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951626</v>
       </c>
       <c r="B2" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957695</v>
       </c>
       <c r="B3" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957699</v>
       </c>
       <c r="B4" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951627</v>
       </c>
       <c r="B5" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136951628</v>
       </c>
       <c r="B6" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136951630</v>
       </c>
       <c r="B7" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136951631</v>
       </c>
       <c r="B8" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136957696</v>
       </c>
       <c r="B9" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136957697</v>
       </c>
       <c r="B10" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136957700</v>
       </c>
       <c r="B11" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136957698</v>
       </c>
       <c r="B12" t="n">
-        <v>108476</v>
+        <v>108480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136951629</v>
       </c>
       <c r="B13" t="n">
-        <v>99355</v>
+        <v>99358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>136957694</v>
       </c>
       <c r="B14" t="n">
-        <v>99355</v>
+        <v>99358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
